--- a/docs/API명세서_v1.0_CKD.xlsx
+++ b/docs/API명세서_v1.0_CKD.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="10" customWidth="1" style="33" min="1" max="1"/>
@@ -5802,44 +5802,44 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>api/v1/auth/password-reset/request</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t>비밀번호 재설정 코드 발급 (REQ-AUTH-C, Rate Limit 5회/분, EMAIL_MODE=demo|production)</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
+      <c r="E58" s="0" t="inlineStr"/>
+      <c r="F58" s="0" t="inlineStr"/>
+      <c r="G58" s="0" t="inlineStr"/>
+      <c r="H58" s="0" t="inlineStr"/>
+      <c r="I58" s="0" t="inlineStr">
         <is>
           <t>{
   "email": {type: str, required: true, format: "RFC 5322"}
 }</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="0" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
+      <c r="K58" s="0" t="inlineStr"/>
+      <c r="L58" s="0" t="inlineStr">
         <is>
           <t>{
   "sent": bool,
@@ -5849,43 +5849,43 @@
 }</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M58" s="0" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N58" s="0" t="inlineStr">
         <is>
           <t>코드 발송 성공 (demo면 demo_code에 6자리 코드 노출)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>api/v1/auth/password-reset/verify</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t>코드 검증 + 임시 비밀번호 발급 (Rate Limit 10회/분, 5회 실패 시 코드 무효화)</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
+      <c r="E59" s="0" t="inlineStr"/>
+      <c r="F59" s="0" t="inlineStr"/>
+      <c r="G59" s="0" t="inlineStr"/>
+      <c r="H59" s="0" t="inlineStr"/>
+      <c r="I59" s="0" t="inlineStr">
         <is>
           <t>{
   "email": {type: str, required: true},
@@ -5893,25 +5893,25 @@
 }</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="0" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
+      <c r="K59" s="0" t="inlineStr"/>
+      <c r="L59" s="0" t="inlineStr">
         <is>
           <t>{
   "temp_password": str
 }</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M59" s="0" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N59" s="0" t="inlineStr">
         <is>
           <t>발급된 임시 비밀번호로 즉시 로그인 가능</t>
         </is>
@@ -7101,6 +7101,198 @@
       </c>
       <c r="P79" s="45" t="n"/>
       <c r="Q79" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>/api/v1/auth/email-verification/request</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-003 이메일 인증 코드 재발송 (PR #9, 1h 3회)</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>200/400/422/429</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>풀스택</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>/api/v1/auth/email-verification/verify</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-003 이메일 인증 코드 검증 (PR #9, 10/분)</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>200/400/404/429</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>풀스택</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>/api/v1/chat/messages</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>REQ-RAG RAG 챗봇 질문/응답 (PR #5, 10/분)</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>200/422/500/504</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>AI+풀스택</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>/api/v1/dashboard/egfr-simulation</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>REQ-DASH-003 예상 eGFR What-if 시뮬레이션 (PR #7) — 명세 v0.8 'POST /simulations/run' 갱신</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>풀스택</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>/api/v1/challenges/slump-micro</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-006 슬럼프 + 오늘의 마이크로 챌린지 (PR #12)</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>200/404</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>풀스택</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>/api/v1/challenges/slump-micro/checkin</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-006 마이크로 챌린지 체크인 (PR #12, 일별 중복 차단)</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>200/400/404</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>풀스택</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
